--- a/data/trans_camb/P12_1_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P12_1_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 17,17</t>
+          <t>4,54; 16,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 18,76</t>
+          <t>4,94; 17,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,62; -4,31</t>
+          <t>-13,58; -4,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,81; 31,45</t>
+          <t>15,75; 31,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,7; 21,5</t>
+          <t>7,87; 22,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,24; -7,61</t>
+          <t>-17,81; -7,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,92; 21,93</t>
+          <t>12,58; 22,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 18,21</t>
+          <t>8,58; 18,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,23; -6,91</t>
+          <t>-14,16; -7,18</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,94; 176,59</t>
+          <t>28,34; 172,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,49; 191,43</t>
+          <t>30,72; 187,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-86,67; -41,98</t>
+          <t>-84,41; -38,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,2; 217,07</t>
+          <t>72,8; 219,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,47; 148,72</t>
+          <t>36,22; 154,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,56; -52,62</t>
+          <t>-80,59; -51,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,24; 169,29</t>
+          <t>71,39; 181,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,75; 139,49</t>
+          <t>47,7; 147,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-79,31; -53,98</t>
+          <t>-78,37; -53,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,97; -6,57</t>
+          <t>-15,74; -6,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,33; -12,61</t>
+          <t>-21,21; -12,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,18; -4,54</t>
+          <t>-15,12; -4,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,27; -9,42</t>
+          <t>-19,96; -8,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,87; -20,79</t>
+          <t>-30,82; -21,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,78; -13,66</t>
+          <t>-23,66; -13,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,81; -9,58</t>
+          <t>-16,7; -9,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,94; -18,2</t>
+          <t>-24,86; -18,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,23; -10,74</t>
+          <t>-18,07; -10,77</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-63,66; -33,38</t>
+          <t>-63,5; -31,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-83,86; -62,61</t>
+          <t>-83,47; -64,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,27; -21,83</t>
+          <t>-61,21; -22,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,45; -29,61</t>
+          <t>-53,7; -28,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,51; -64,7</t>
+          <t>-80,78; -65,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,27; -42,61</t>
+          <t>-62,35; -43,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,57; -35,14</t>
+          <t>-54,63; -33,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,3; -67,79</t>
+          <t>-80,52; -67,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,84; -39,95</t>
+          <t>-59,79; -39,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 12,4</t>
+          <t>3,29; 12,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 10,23</t>
+          <t>1,45; 10,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 6,8</t>
+          <t>-1,11; 7,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 19,66</t>
+          <t>8,23; 19,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 11,15</t>
+          <t>1,41; 11,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,48</t>
+          <t>1,01; 9,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 14,46</t>
+          <t>7,42; 14,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 9,17</t>
+          <t>2,97; 9,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,22</t>
+          <t>1,12; 6,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,69; 310,35</t>
+          <t>39,04; 298,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,33; 252,7</t>
+          <t>14,67; 241,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 171,96</t>
+          <t>-14,96; 175,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68,4; 284,87</t>
+          <t>70,16; 284,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,02; 173,65</t>
+          <t>11,45; 196,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,34; 146,87</t>
+          <t>5,06; 140,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,98; 250,5</t>
+          <t>80,18; 234,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,47; 152,94</t>
+          <t>31,97; 155,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,39; 122,84</t>
+          <t>10,73; 111,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 9,96</t>
+          <t>-1,25; 9,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 9,66</t>
+          <t>-1,13; 9,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 7,78</t>
+          <t>-4,13; 7,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,62; 23,45</t>
+          <t>11,36; 23,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 14,13</t>
+          <t>1,91; 14,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 0,45</t>
+          <t>-12,08; 0,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,78; 15,32</t>
+          <t>6,92; 15,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,57</t>
+          <t>2,25; 10,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 2,79</t>
+          <t>-6,33; 2,39</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 94,6</t>
+          <t>-9,41; 91,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 88,74</t>
+          <t>-7,71; 84,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 69,65</t>
+          <t>-26,63; 69,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49,14; 147,83</t>
+          <t>51,03; 151,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,87; 89,69</t>
+          <t>7,79; 87,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,79; 2,56</t>
+          <t>-55,7; 4,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,99; 110,15</t>
+          <t>37,33; 106,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,94; 74,4</t>
+          <t>12,26; 73,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,81; 19,44</t>
+          <t>-35,44; 16,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,95; -6,26</t>
+          <t>-21,43; -7,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 3,06</t>
+          <t>-13,03; 2,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,74; 23,18</t>
+          <t>5,1; 22,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 3,18</t>
+          <t>-14,36; 3,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -0,21</t>
+          <t>-18,29; -0,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,04; 24,32</t>
+          <t>7,5; 24,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,55; -3,45</t>
+          <t>-15,37; -3,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,38; -1,69</t>
+          <t>-12,81; -1,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,43; 20,89</t>
+          <t>9,56; 21,46</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-73,41; -29,94</t>
+          <t>-74,14; -33,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 15,97</t>
+          <t>-44,74; 16,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19,96; 117,16</t>
+          <t>17,96; 113,76</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-39,35; 11,45</t>
+          <t>-39,15; 12,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-48,87; -0,8</t>
+          <t>-50,22; -2,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,94; 91,28</t>
+          <t>19,8; 93,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-49,76; -13,86</t>
+          <t>-49,49; -14,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,15; -6,37</t>
+          <t>-40,51; -6,22</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28,79; 82,96</t>
+          <t>29,53; 85,87</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 9,73</t>
+          <t>-1,29; 9,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 6,04</t>
+          <t>-3,81; 6,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 8,29</t>
+          <t>-1,66; 8,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,34; 14,91</t>
+          <t>2,06; 15,08</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 10,84</t>
+          <t>-1,84; 11,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 6,31</t>
+          <t>-3,95; 6,16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,32; 11,36</t>
+          <t>2,36; 10,74</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 6,95</t>
+          <t>-1,43; 6,63</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 6,0</t>
+          <t>-1,31; 6,13</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 124,53</t>
+          <t>-11,87; 131,98</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 82,07</t>
+          <t>-31,0; 83,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 114,59</t>
+          <t>-12,99; 116,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15,32; 136,14</t>
+          <t>9,8; 133,93</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 93,87</t>
+          <t>-11,69; 98,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 57,0</t>
+          <t>-23,62; 55,74</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,73; 109,78</t>
+          <t>16,86; 102,79</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 66,31</t>
+          <t>-9,71; 65,35</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 58,86</t>
+          <t>-10,88; 59,46</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,32; 9,15</t>
+          <t>1,5; 9,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 5,4</t>
+          <t>-2,02; 5,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,3; 10,58</t>
+          <t>1,8; 10,16</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,53; 10,7</t>
+          <t>1,5; 10,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 4,25</t>
+          <t>-4,23; 4,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,86; 55,58</t>
+          <t>8,75; 56,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,65</t>
+          <t>2,83; 8,99</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 3,92</t>
+          <t>-1,83; 3,94</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7,37; 46,67</t>
+          <t>7,05; 42,65</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>8,52; 89,86</t>
+          <t>11,0; 99,61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 56,79</t>
+          <t>-14,95; 56,24</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16,1; 107,63</t>
+          <t>11,23; 97,82</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,33; 71,56</t>
+          <t>8,61; 68,75</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 28,45</t>
+          <t>-22,36; 29,25</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>49,11; 394,79</t>
+          <t>47,75; 390,57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,81; 65,39</t>
+          <t>18,6; 71,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 29,84</t>
+          <t>-11,52; 30,79</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>49,82; 366,95</t>
+          <t>46,67; 318,29</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,65; -5,37</t>
+          <t>-14,09; -5,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-24,88; -18,15</t>
+          <t>-24,79; -17,67</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-24,57; -14,44</t>
+          <t>-24,23; -14,12</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 0,47</t>
+          <t>-8,7; -0,19</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-22,97; -15,31</t>
+          <t>-22,94; -15,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,02; -6,86</t>
+          <t>-15,05; -7,11</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -3,72</t>
+          <t>-10,13; -3,95</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-22,63; -17,35</t>
+          <t>-22,86; -17,46</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-20,49; -12,22</t>
+          <t>-20,77; -12,09</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-49,02; -22,27</t>
+          <t>-49,81; -22,86</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-86,83; -74,8</t>
+          <t>-86,24; -73,11</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-87,2; -58,11</t>
+          <t>-87,17; -57,22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 1,83</t>
+          <t>-28,96; -0,88</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-76,14; -59,53</t>
+          <t>-76,34; -59,2</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-48,95; -26,03</t>
+          <t>-48,81; -27,71</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -14,07</t>
+          <t>-35,06; -15,11</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-79,3; -68,5</t>
+          <t>-79,02; -68,18</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-72,43; -46,96</t>
+          <t>-73,52; -46,19</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,61</t>
+          <t>-3,03; 0,74</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -3,5</t>
+          <t>-7,05; -3,58</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -2,44</t>
+          <t>-7,39; -2,42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,88</t>
+          <t>1,54; 5,6</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,71; -3,86</t>
+          <t>-7,58; -3,87</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 15,33</t>
+          <t>-4,1; 16,55</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,63</t>
+          <t>-0,13; 2,71</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,77; -4,24</t>
+          <t>-6,79; -4,21</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 6,37</t>
+          <t>-4,6; 7,13</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 3,99</t>
+          <t>-17,19; 4,68</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -21,84</t>
+          <t>-39,67; -22,97</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-42,48; -15,11</t>
+          <t>-42,83; -15,18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5,97; 27,48</t>
+          <t>6,57; 25,85</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-32,82; -18,08</t>
+          <t>-32,31; -17,12</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 68,27</t>
+          <t>-18,05; 74,73</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 13,74</t>
+          <t>-0,68; 14,2</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-33,16; -22,08</t>
+          <t>-33,21; -21,98</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 32,19</t>
+          <t>-23,09; 37,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_1_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P12_1_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-8,67</t>
+          <t>-9,04</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-12,29</t>
+          <t>-12,34</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-10,45</t>
+          <t>-10,63</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 16,83</t>
+          <t>4,73; 17,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 17,62</t>
+          <t>4,95; 17,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,58; -4,36</t>
+          <t>-13,48; -4,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,75; 31,09</t>
+          <t>15,65; 31,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 22,59</t>
+          <t>7,37; 22,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,81; -7,69</t>
+          <t>-17,06; -7,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,58; 22,78</t>
+          <t>11,71; 22,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,58; 18,37</t>
+          <t>8,25; 18,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -7,18</t>
+          <t>-14,43; -7,36</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-69,5%</t>
+          <t>-72,46%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-68,95%</t>
+          <t>-69,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-69,26%</t>
+          <t>-70,47%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,34; 172,63</t>
+          <t>27,07; 172,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,72; 187,3</t>
+          <t>33,2; 186,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-84,41; -38,04</t>
+          <t>-85,8; -48,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,8; 219,69</t>
+          <t>73,51; 225,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,22; 154,08</t>
+          <t>33,71; 159,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,59; -51,59</t>
+          <t>-79,83; -51,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,39; 181,9</t>
+          <t>66,92; 176,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,7; 147,42</t>
+          <t>47,41; 145,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-78,37; -53,83</t>
+          <t>-79,25; -56,98</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-10,14</t>
+          <t>-10,06</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-18,65</t>
+          <t>-18,6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-14,47</t>
+          <t>-14,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,74; -6,45</t>
+          <t>-16,45; -7,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,21; -12,61</t>
+          <t>-21,03; -12,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,12; -4,74</t>
+          <t>-15,33; -5,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,96; -8,96</t>
+          <t>-20,22; -9,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,82; -21,06</t>
+          <t>-30,6; -20,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,66; -13,74</t>
+          <t>-24,17; -14,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,7; -9,09</t>
+          <t>-16,67; -9,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,86; -18,13</t>
+          <t>-24,66; -18,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,07; -10,77</t>
+          <t>-17,96; -10,68</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-45,14%</t>
+          <t>-44,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-53,39%</t>
+          <t>-53,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-50,3%</t>
+          <t>-49,95%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-63,5; -31,6</t>
+          <t>-64,79; -34,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-83,47; -64,28</t>
+          <t>-83,96; -64,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,21; -22,33</t>
+          <t>-60,54; -23,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,7; -28,7</t>
+          <t>-54,15; -28,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,78; -65,06</t>
+          <t>-81,15; -65,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,35; -43,05</t>
+          <t>-62,81; -43,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,63; -33,79</t>
+          <t>-54,65; -34,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,52; -67,61</t>
+          <t>-80,06; -67,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,79; -39,8</t>
+          <t>-57,69; -39,46</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>3,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,97</t>
+          <t>3,65; 12,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 10,19</t>
+          <t>1,38; 10,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 7,32</t>
+          <t>-1,5; 6,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,23; 19,13</t>
+          <t>8,25; 19,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 11,68</t>
+          <t>1,33; 11,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,3</t>
+          <t>0,74; 9,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 14,58</t>
+          <t>7,43; 14,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 9,42</t>
+          <t>2,87; 9,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,77</t>
+          <t>1,28; 6,47</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,04; 298,49</t>
+          <t>45,96; 320,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,67; 241,76</t>
+          <t>14,42; 240,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 175,83</t>
+          <t>-21,38; 150,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>70,16; 284,69</t>
+          <t>74,03; 283,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,45; 196,92</t>
+          <t>10,58; 162,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,06; 140,98</t>
+          <t>6,64; 145,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80,18; 234,81</t>
+          <t>85,37; 244,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,97; 155,14</t>
+          <t>31,36; 155,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,73; 111,68</t>
+          <t>14,3; 109,05</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,76</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-0,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 9,92</t>
+          <t>-0,91; 9,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 9,12</t>
+          <t>-0,92; 9,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 7,86</t>
+          <t>-4,72; 7,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,36; 23,59</t>
+          <t>11,13; 23,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 14,03</t>
+          <t>2,26; 14,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 0,87</t>
+          <t>-6,51; 3,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,92; 15,33</t>
+          <t>6,56; 15,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 10,43</t>
+          <t>2,19; 10,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 2,39</t>
+          <t>-3,51; 4,14</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-25,63%</t>
+          <t>-6,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-10,0%</t>
+          <t>-0,42%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 91,76</t>
+          <t>-7,39; 94,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 84,56</t>
+          <t>-6,56; 89,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 69,74</t>
+          <t>-30,9; 63,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51,03; 151,68</t>
+          <t>53,32; 149,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,79; 87,79</t>
+          <t>10,34; 93,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,7; 4,83</t>
+          <t>-29,07; 25,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,33; 106,77</t>
+          <t>37,61; 108,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,26; 73,92</t>
+          <t>11,9; 72,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 16,14</t>
+          <t>-20,04; 30,12</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14,01</t>
+          <t>12,94</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,47</t>
+          <t>15,7</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,59</t>
+          <t>14,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,43; -7,14</t>
+          <t>-20,73; -6,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 2,86</t>
+          <t>-12,66; 3,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,1; 22,52</t>
+          <t>4,2; 21,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 3,28</t>
+          <t>-14,69; 3,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,29; -0,63</t>
+          <t>-19,29; -1,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 24,26</t>
+          <t>7,35; 22,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,37; -3,73</t>
+          <t>-15,07; -3,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -1,71</t>
+          <t>-13,29; -1,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,56; 21,46</t>
+          <t>8,46; 20,53</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-74,14; -33,15</t>
+          <t>-74,18; -31,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 16,99</t>
+          <t>-45,01; 15,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17,96; 113,76</t>
+          <t>13,81; 106,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 12,24</t>
+          <t>-40,99; 11,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-50,22; -2,35</t>
+          <t>-50,73; -5,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,8; 93,0</t>
+          <t>19,44; 87,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-49,49; -14,46</t>
+          <t>-47,56; -12,91</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-40,51; -6,22</t>
+          <t>-42,3; -5,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29,53; 85,87</t>
+          <t>25,77; 82,44</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>1,87</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 9,96</t>
+          <t>-1,58; 9,83</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 6,11</t>
+          <t>-4,11; 5,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 8,64</t>
+          <t>-2,34; 7,51</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,06; 15,08</t>
+          <t>2,76; 14,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 11,26</t>
+          <t>-1,82; 11,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 6,16</t>
+          <t>-4,41; 6,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,74</t>
+          <t>2,38; 11,04</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 6,63</t>
+          <t>-1,26; 7,25</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 6,13</t>
+          <t>-1,8; 5,43</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 131,98</t>
+          <t>-14,72; 129,61</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 83,67</t>
+          <t>-33,03; 79,08</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 116,85</t>
+          <t>-18,08; 104,08</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9,8; 133,93</t>
+          <t>15,41; 129,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 98,36</t>
+          <t>-11,41; 101,87</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 55,74</t>
+          <t>-25,08; 59,21</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,86; 102,79</t>
+          <t>16,42; 107,35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 65,35</t>
+          <t>-9,73; 74,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 59,46</t>
+          <t>-13,91; 53,14</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6,1</t>
+          <t>6,0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,69</t>
+          <t>9,54</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18,91</t>
+          <t>7,88</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,37</t>
+          <t>1,5; 9,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 5,69</t>
+          <t>-2,58; 5,58</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,8; 10,16</t>
+          <t>1,96; 10,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,5; 10,44</t>
+          <t>1,46; 10,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 4,33</t>
+          <t>-4,17; 4,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,75; 56,32</t>
+          <t>4,92; 13,9</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,83; 8,99</t>
+          <t>2,94; 9,2</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,94</t>
+          <t>-1,7; 3,8</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7,05; 42,65</t>
+          <t>4,83; 10,83</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>161,66%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>130,74%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>11,0; 99,61</t>
+          <t>10,55; 97,3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 56,24</t>
+          <t>-18,63; 57,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11,23; 97,82</t>
+          <t>13,31; 103,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8,61; 68,75</t>
+          <t>6,24; 69,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 29,25</t>
+          <t>-21,38; 28,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>47,75; 390,57</t>
+          <t>24,95; 92,69</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,6; 71,01</t>
+          <t>18,32; 71,58</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 30,79</t>
+          <t>-11,13; 30,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>46,67; 318,29</t>
+          <t>30,16; 82,96</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-18,86</t>
+          <t>-16,55</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-10,96</t>
+          <t>-10,75</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-15,54</t>
+          <t>-13,6</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-14,09; -5,6</t>
+          <t>-14,56; -5,34</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-24,79; -17,67</t>
+          <t>-24,88; -17,56</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-24,23; -14,12</t>
+          <t>-20,43; -12,67</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-8,7; -0,19</t>
+          <t>-8,8; 0,17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-22,94; -15,0</t>
+          <t>-23,36; -15,42</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -7,11</t>
+          <t>-14,83; -6,67</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -3,95</t>
+          <t>-10,06; -3,87</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-22,86; -17,46</t>
+          <t>-22,67; -17,3</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-20,77; -12,09</t>
+          <t>-16,42; -10,99</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-71,77%</t>
+          <t>-63,0%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-39,22%</t>
+          <t>-38,48%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-57,29%</t>
+          <t>-50,12%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-49,81; -22,86</t>
+          <t>-49,95; -22,02</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-86,24; -73,11</t>
+          <t>-86,74; -73,38</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-87,17; -57,22</t>
+          <t>-71,27; -52,42</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-28,96; -0,88</t>
+          <t>-29,77; 0,89</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-76,34; -59,2</t>
+          <t>-76,34; -59,57</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-48,81; -27,71</t>
+          <t>-49,32; -27,06</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-35,06; -15,11</t>
+          <t>-34,63; -15,11</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-79,02; -68,18</t>
+          <t>-79,09; -68,24</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-73,52; -46,19</t>
+          <t>-56,82; -42,76</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-4,35</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>-2,89</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-3,18</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,74</t>
+          <t>-2,94; 0,83</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -3,58</t>
+          <t>-6,95; -3,41</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -2,42</t>
+          <t>-5,22; -1,69</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,6</t>
+          <t>1,65; 5,94</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -3,87</t>
+          <t>-7,73; -3,91</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 16,55</t>
+          <t>-4,91; -1,04</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,71</t>
+          <t>-0,11; 2,69</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,79; -4,21</t>
+          <t>-6,75; -4,21</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 7,13</t>
+          <t>-4,53; -1,92</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-25,71%</t>
+          <t>-21,04%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>-12,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-7,75%</t>
+          <t>-16,16%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 4,68</t>
+          <t>-16,69; 4,84</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -22,97</t>
+          <t>-38,7; -21,26</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-42,83; -15,18</t>
+          <t>-29,44; -10,59</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6,57; 25,85</t>
+          <t>7,11; 27,76</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-32,31; -17,12</t>
+          <t>-33,12; -18,32</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 74,73</t>
+          <t>-20,72; -4,9</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 14,2</t>
+          <t>-0,55; 14,05</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-33,21; -21,98</t>
+          <t>-33,27; -22,0</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 37,13</t>
+          <t>-22,08; -10,02</t>
         </is>
       </c>
     </row>
